--- a/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
+++ b/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\endo-learn\BGBSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\endo-learn\BGBSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{64CF225A-7568-4778-89A3-1CD84988F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF5F758-E175-41FC-8728-39F16D0BA183}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD3F269-C4F9-4F94-B2EA-361B010723F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="max">#REF!</definedName>
     <definedName name="min">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -76,10 +76,70 @@
     <t>Sources:</t>
   </si>
   <si>
+    <t>BNEF Data</t>
+  </si>
+  <si>
+    <t>Global EV Li-Ion Battery Demand (GWh)</t>
+  </si>
+  <si>
+    <t>New EV Sales (Number of Vehicles)</t>
+  </si>
+  <si>
+    <t>Global battery cap (MWh)</t>
+  </si>
+  <si>
+    <t>For grid batteries, we will use BNEF NEO numbers and curve fit to extrapolate</t>
+  </si>
+  <si>
+    <t>Bloomberg</t>
+  </si>
+  <si>
+    <t>for years 2014-2050.  We assume no grid batteries retire during the model</t>
+  </si>
+  <si>
+    <t>run, so installed capacity equals cumulative capacity.</t>
+  </si>
+  <si>
+    <t>For Evs, we use Bloomberg New Energy Finance's numbers.  This assumes an aggressive rate of EV deployment,</t>
+  </si>
+  <si>
+    <t>which matches usual EPS model behavior in the United States and other EPS regions we've tested.</t>
+  </si>
+  <si>
+    <t>Grid battery capacity (MWh)</t>
+  </si>
+  <si>
+    <t>EV battery new sales (MWh)</t>
+  </si>
+  <si>
+    <t>New EV Sales, Extrapolated (Number of Vehicles)</t>
+  </si>
+  <si>
+    <t>Executive Summary</t>
+  </si>
+  <si>
+    <t>EV sales</t>
+  </si>
+  <si>
     <t>Grid batteries through 2030</t>
   </si>
   <si>
-    <t>Bloomberg</t>
+    <t>Raw Data</t>
+  </si>
+  <si>
+    <t>BNEF - Long-Term Electric Vehicle Outlook 2024</t>
+  </si>
+  <si>
+    <t>EV cumulative battery capacity</t>
+  </si>
+  <si>
+    <t>GW to GWh, assuming 4 hour battery capacity</t>
+  </si>
+  <si>
+    <t>Cumulative GW Capacity</t>
+  </si>
+  <si>
+    <t>Cumulative GWh Capacity</t>
   </si>
   <si>
     <t>New Energy Outlook 2024</t>
@@ -91,70 +151,10 @@
     <t>Data Viewer</t>
   </si>
   <si>
-    <t>EV sales</t>
-  </si>
-  <si>
     <t>Electric Vehicle Outlook 2024</t>
   </si>
   <si>
     <t>https://about.bnef.com/electric-vehicle-outlook/</t>
-  </si>
-  <si>
-    <t>Executive Summary</t>
-  </si>
-  <si>
-    <t>GW to GWh, assuming 4 hour battery capacity</t>
-  </si>
-  <si>
-    <t>Cumulative GW Capacity</t>
-  </si>
-  <si>
-    <t>Cumulative GWh Capacity</t>
-  </si>
-  <si>
-    <t>Raw Data</t>
-  </si>
-  <si>
-    <t>BNEF Data</t>
-  </si>
-  <si>
-    <t>BNEF - Long-Term Electric Vehicle Outlook 2024</t>
-  </si>
-  <si>
-    <t>Global EV Li-Ion Battery Demand (GWh)</t>
-  </si>
-  <si>
-    <t>New EV Sales (Number of Vehicles)</t>
-  </si>
-  <si>
-    <t>New EV Sales, Extrapolated (Number of Vehicles)</t>
-  </si>
-  <si>
-    <t>For grid batteries, we will use BNEF NEO numbers and curve fit to extrapolate</t>
-  </si>
-  <si>
-    <t>for years 2014-2050.  We assume no grid batteries retire during the model</t>
-  </si>
-  <si>
-    <t>run, so installed capacity equals cumulative capacity.</t>
-  </si>
-  <si>
-    <t>Grid battery capacity (MWh)</t>
-  </si>
-  <si>
-    <t>For Evs, we use Bloomberg New Energy Finance's numbers.  This assumes an aggressive rate of EV deployment,</t>
-  </si>
-  <si>
-    <t>which matches usual EPS model behavior in the United States and other EPS regions we've tested.</t>
-  </si>
-  <si>
-    <t>EV battery new sales (MWh)</t>
-  </si>
-  <si>
-    <t>EV cumulative battery capacity</t>
-  </si>
-  <si>
-    <t>Global battery cap (MWh)</t>
   </si>
 </sst>
 </file>
@@ -165,7 +165,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,7 +228,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,6 +238,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -268,7 +274,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -300,9 +306,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Table Header 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
@@ -323,7 +330,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -697,6 +704,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -704,7 +712,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -742,7 +749,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2838,80 +2845,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="9">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="9">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
     </row>
   </sheetData>
@@ -2923,23 +2930,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B1">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2020</v>
       </c>
@@ -3034,9 +3041,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>13.247281105915055</v>
@@ -3132,9 +3139,9 @@
         <v>3018.3651290394619</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <f>B4*$B$1</f>
@@ -3269,7 +3276,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AF16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.7109375" customWidth="1"/>
@@ -3288,7 +3295,7 @@
     <col min="30" max="31" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3296,7 +3303,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2020</v>
       </c>
@@ -3319,9 +3326,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>150082678.90546128</v>
@@ -3345,14 +3352,14 @@
         <v>3630152910.6631694</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="23.25">
+    <row r="10" spans="1:32" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6">
         <v>2020</v>
@@ -3448,9 +3455,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B12" s="11" cm="1">
         <f t="array" ref="B12">TREND($B$8:$C$8,$B$7:$C$7,B11)/10^6</f>
@@ -3577,9 +3584,9 @@
         <v>3630.1529106631624</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3602,9 +3609,9 @@
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B14" s="8">
         <f>B16</f>
@@ -3731,7 +3738,7 @@
         <v>81549620.895449489</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="14">
@@ -3775,7 +3782,7 @@
       <c r="AE15" s="12"/>
       <c r="AF15" s="12"/>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B16" s="8">
         <f t="shared" ref="B16:AF16" si="1" xml:space="preserve"> (83.94318 + (-3.575905 - 83.94318)/(1 + (B11/2030.462)^372.9304))*1000000</f>
         <v>7551143.5426923158</v>
@@ -3911,7 +3918,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AG15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.42578125" customWidth="1"/>
     <col min="2" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -3920,22 +3927,22 @@
     <col min="7" max="32" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2020</v>
       </c>
@@ -4030,9 +4037,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <f>'Grid Battery Storage'!B5*1000</f>
@@ -4159,17 +4166,17 @@
         <v>12073460.516157847</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2020</v>
       </c>
@@ -4264,9 +4271,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B12" s="16">
         <f>'EV Batteries'!B12*1000</f>
@@ -4394,9 +4401,9 @@
       </c>
       <c r="AG12" s="16"/>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B13" s="16">
         <f>SUM($B12:B12)</f>
@@ -4523,7 +4530,7 @@
         <v>84210167.376524493</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AF15" s="16"/>
     </row>
   </sheetData>
@@ -4539,25 +4546,25 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8">
-        <f>Summary!B6+Summary!B13</f>
-        <v>203071.80332911675</v>
+        <f>BGBSC!B2</f>
+        <v>563553.04625794571</v>
       </c>
     </row>
   </sheetData>
@@ -4570,16 +4577,16 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:BE2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="51" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="33" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -4731,9 +4738,9 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:57">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8">
         <f>Summary!C6+Summary!C13</f>
@@ -4855,85 +4862,85 @@
         <f>Summary!AF6+Summary!AF13</f>
         <v>96283627.892682344</v>
       </c>
-      <c r="AF2" s="8">
-        <f>AE2+AE2-AD2</f>
-        <v>100323940.9654686</v>
-      </c>
-      <c r="AG2" s="8">
-        <f t="shared" ref="AG2:AY2" si="0">AF2+AF2-AE2</f>
-        <v>104364254.03825486</v>
-      </c>
-      <c r="AH2" s="8">
-        <f t="shared" si="0"/>
-        <v>108404567.11104111</v>
-      </c>
-      <c r="AI2" s="8">
-        <f t="shared" si="0"/>
-        <v>112444880.18382737</v>
-      </c>
-      <c r="AJ2" s="8">
-        <f t="shared" si="0"/>
-        <v>116485193.25661363</v>
-      </c>
-      <c r="AK2" s="8">
-        <f t="shared" si="0"/>
-        <v>120525506.32939988</v>
-      </c>
-      <c r="AL2" s="8">
-        <f t="shared" si="0"/>
-        <v>124565819.40218614</v>
-      </c>
-      <c r="AM2" s="8">
-        <f t="shared" si="0"/>
-        <v>128606132.4749724</v>
-      </c>
-      <c r="AN2" s="8">
-        <f t="shared" si="0"/>
-        <v>132646445.54775865</v>
-      </c>
-      <c r="AO2" s="8">
-        <f t="shared" si="0"/>
-        <v>136686758.62054491</v>
-      </c>
-      <c r="AP2" s="8">
-        <f t="shared" si="0"/>
-        <v>140727071.69333118</v>
-      </c>
-      <c r="AQ2" s="8">
-        <f t="shared" si="0"/>
-        <v>144767384.76611745</v>
-      </c>
-      <c r="AR2" s="8">
-        <f t="shared" si="0"/>
-        <v>148807697.83890373</v>
-      </c>
-      <c r="AS2" s="8">
-        <f t="shared" si="0"/>
-        <v>152848010.91169</v>
-      </c>
-      <c r="AT2" s="8">
-        <f t="shared" si="0"/>
-        <v>156888323.98447627</v>
-      </c>
-      <c r="AU2" s="8">
-        <f t="shared" si="0"/>
-        <v>160928637.05726254</v>
-      </c>
-      <c r="AV2" s="8">
-        <f t="shared" si="0"/>
-        <v>164968950.13004881</v>
-      </c>
-      <c r="AW2" s="8">
-        <f t="shared" si="0"/>
-        <v>169009263.20283508</v>
-      </c>
-      <c r="AX2" s="8">
-        <f t="shared" si="0"/>
-        <v>173049576.27562135</v>
-      </c>
-      <c r="AY2" s="8">
-        <f t="shared" si="0"/>
-        <v>177089889.34840763</v>
+      <c r="AF2" s="18">
+        <f>_xlfn.FORECAST.LINEAR(AF1,$U$2:$AE$2,$U$1:$AE$1)</f>
+        <v>100761933.46525288</v>
+      </c>
+      <c r="AG2" s="18">
+        <f t="shared" ref="AG2:AY2" si="0">_xlfn.FORECAST.LINEAR(AG1,$U$2:$AE$2,$U$1:$AE$1)</f>
+        <v>104979579.90484715</v>
+      </c>
+      <c r="AH2" s="18">
+        <f t="shared" si="0"/>
+        <v>109197226.34444332</v>
+      </c>
+      <c r="AI2" s="18">
+        <f t="shared" si="0"/>
+        <v>113414872.78403759</v>
+      </c>
+      <c r="AJ2" s="18">
+        <f t="shared" si="0"/>
+        <v>117632519.22363186</v>
+      </c>
+      <c r="AK2" s="18">
+        <f t="shared" si="0"/>
+        <v>121850165.66322803</v>
+      </c>
+      <c r="AL2" s="18">
+        <f t="shared" si="0"/>
+        <v>126067812.1028223</v>
+      </c>
+      <c r="AM2" s="18">
+        <f t="shared" si="0"/>
+        <v>130285458.54241657</v>
+      </c>
+      <c r="AN2" s="18">
+        <f t="shared" si="0"/>
+        <v>134503104.98201275</v>
+      </c>
+      <c r="AO2" s="18">
+        <f t="shared" si="0"/>
+        <v>138720751.42160702</v>
+      </c>
+      <c r="AP2" s="18">
+        <f t="shared" si="0"/>
+        <v>142938397.86120129</v>
+      </c>
+      <c r="AQ2" s="18">
+        <f t="shared" si="0"/>
+        <v>147156044.30079746</v>
+      </c>
+      <c r="AR2" s="18">
+        <f t="shared" si="0"/>
+        <v>151373690.74039173</v>
+      </c>
+      <c r="AS2" s="18">
+        <f t="shared" si="0"/>
+        <v>155591337.179986</v>
+      </c>
+      <c r="AT2" s="18">
+        <f t="shared" si="0"/>
+        <v>159808983.61958218</v>
+      </c>
+      <c r="AU2" s="18">
+        <f t="shared" si="0"/>
+        <v>164026630.05917645</v>
+      </c>
+      <c r="AV2" s="18">
+        <f t="shared" si="0"/>
+        <v>168244276.49877071</v>
+      </c>
+      <c r="AW2" s="18">
+        <f t="shared" si="0"/>
+        <v>172461922.93836498</v>
+      </c>
+      <c r="AX2" s="18">
+        <f t="shared" si="0"/>
+        <v>176679569.37796116</v>
+      </c>
+      <c r="AY2" s="18">
+        <f t="shared" si="0"/>
+        <v>180897215.81755543</v>
       </c>
       <c r="AZ2" s="8"/>
       <c r="BA2" s="8"/>
@@ -4942,206 +4949,7 @@
       <c r="BD2" s="8"/>
       <c r="BE2" s="8"/>
     </row>
-    <row r="3" spans="1:57">
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="8"/>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8"/>
-      <c r="AQ3" s="8"/>
-      <c r="AR3" s="8"/>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="8"/>
-      <c r="AU3" s="8"/>
-      <c r="AV3" s="8"/>
-      <c r="AW3" s="8"/>
-      <c r="AX3" s="8"/>
-      <c r="AY3" s="8"/>
-      <c r="AZ3" s="8"/>
-      <c r="BA3" s="8"/>
-      <c r="BB3" s="8"/>
-      <c r="BC3" s="8"/>
-      <c r="BD3" s="8"/>
-      <c r="BE3" s="8"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2E22572-1D42-4C90-8638-5056ACFB41B3}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F535230D-C34F-4711-ADDA-6FBCB3126C01}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ECC430A-5FC0-4CB6-B845-612E06EEBD57}"/>
 </file>